--- a/poll_averages.xlsx
+++ b/poll_averages.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S534"/>
+  <dimension ref="A1:S481"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23807,3554 +23807,987 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B461" s="2" t="n">
-        <v>46133</v>
+        <v>46124</v>
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Survation</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D461" t="n">
-        <v>1008</v>
+        <v>3162</v>
       </c>
       <c r="E461" t="b">
         <v>0</v>
       </c>
-      <c r="F461" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G461" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H461" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I461" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J461" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K461" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
       <c r="L461" t="inlineStr"/>
-      <c r="M461" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N461" t="inlineStr"/>
-      <c r="O461" t="inlineStr"/>
-      <c r="P461" t="inlineStr"/>
-      <c r="Q461" t="inlineStr"/>
-      <c r="R461" t="inlineStr"/>
-      <c r="S461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="O461" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P461" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R461" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S461" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B462" s="2" t="n">
-        <v>46112</v>
+        <v>46041</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D462" t="n">
-        <v>1030</v>
+        <v>2975</v>
       </c>
       <c r="E462" t="b">
         <v>0</v>
       </c>
-      <c r="F462" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G462" t="n">
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O462" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P462" t="n">
         <v>0.11</v>
       </c>
-      <c r="H462" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I462" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J462" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K462" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="L462" t="inlineStr"/>
-      <c r="M462" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N462" t="inlineStr"/>
-      <c r="O462" t="inlineStr"/>
-      <c r="P462" t="inlineStr"/>
-      <c r="Q462" t="inlineStr"/>
-      <c r="R462" t="inlineStr"/>
-      <c r="S462" t="inlineStr"/>
+      <c r="Q462" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="R462" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S462" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B463" s="2" t="n">
-        <v>46087</v>
+        <v>45950</v>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>Lord Ashcroft Polls  [ a ] [ b ]</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D463" t="n">
-        <v>2089</v>
+        <v>2908</v>
       </c>
       <c r="E463" t="b">
         <v>0</v>
       </c>
-      <c r="F463" t="n">
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
+      <c r="N463" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O463" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P463" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R463" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S463" t="n">
         <v>0.13</v>
       </c>
-      <c r="G463" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H463" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I463" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J463" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K463" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="L463" t="inlineStr"/>
-      <c r="M463" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N463" t="inlineStr"/>
-      <c r="O463" t="inlineStr"/>
-      <c r="P463" t="inlineStr"/>
-      <c r="Q463" t="inlineStr"/>
-      <c r="R463" t="inlineStr"/>
-      <c r="S463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B464" s="2" t="n">
-        <v>46079</v>
+        <v>45880</v>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D464" t="n">
-        <v>1096</v>
+        <v>3028</v>
       </c>
       <c r="E464" t="b">
         <v>0</v>
       </c>
-      <c r="F464" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G464" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H464" t="n">
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O464" t="n">
         <v>0.17</v>
       </c>
-      <c r="I464" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J464" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K464" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L464" t="inlineStr"/>
-      <c r="M464" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N464" t="inlineStr"/>
-      <c r="O464" t="inlineStr"/>
-      <c r="P464" t="inlineStr"/>
-      <c r="Q464" t="inlineStr"/>
-      <c r="R464" t="inlineStr"/>
-      <c r="S464" t="inlineStr"/>
+      <c r="P464" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R464" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S464" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B465" s="2" t="n">
-        <v>46072</v>
+        <v>45796</v>
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Find Out Now</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D465" t="n">
-        <v>1002</v>
+        <v>2755</v>
       </c>
       <c r="E465" t="b">
         <v>0</v>
       </c>
-      <c r="F465" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G465" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H465" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I465" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J465" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K465" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
       <c r="L465" t="inlineStr"/>
       <c r="M465" t="inlineStr"/>
-      <c r="N465" t="inlineStr"/>
-      <c r="O465" t="inlineStr"/>
-      <c r="P465" t="inlineStr"/>
-      <c r="Q465" t="inlineStr"/>
-      <c r="R465" t="inlineStr"/>
-      <c r="S465" t="inlineStr"/>
+      <c r="N465" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="O465" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P465" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R465" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="S465" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B466" s="2" t="n">
-        <v>46071</v>
+        <v>45705</v>
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>YouGov</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D466" t="n">
-        <v>1517</v>
+        <v>3001</v>
       </c>
       <c r="E466" t="b">
         <v>0</v>
       </c>
-      <c r="F466" t="n">
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="O466" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P466" t="n">
         <v>0.14</v>
       </c>
-      <c r="G466" t="n">
+      <c r="Q466" t="n">
         <v>0.11</v>
       </c>
-      <c r="H466" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I466" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J466" t="n">
+      <c r="R466" t="n">
         <v>0.11</v>
       </c>
-      <c r="K466" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L466" t="inlineStr"/>
-      <c r="M466" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N466" t="inlineStr"/>
-      <c r="O466" t="inlineStr"/>
-      <c r="P466" t="inlineStr"/>
-      <c r="Q466" t="inlineStr"/>
-      <c r="R466" t="inlineStr"/>
-      <c r="S466" t="inlineStr"/>
+      <c r="S466" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B467" s="2" t="n">
-        <v>46066</v>
+        <v>45600</v>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Norstat</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D467" t="n">
-        <v>1001</v>
+        <v>3209</v>
       </c>
       <c r="E467" t="b">
         <v>0</v>
       </c>
-      <c r="F467" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G467" t="n">
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O467" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="P467" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R467" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S467" t="n">
         <v>0.11</v>
       </c>
-      <c r="H467" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I467" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J467" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K467" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L467" t="inlineStr"/>
-      <c r="M467" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N467" t="inlineStr"/>
-      <c r="O467" t="inlineStr"/>
-      <c r="P467" t="inlineStr"/>
-      <c r="Q467" t="inlineStr"/>
-      <c r="R467" t="inlineStr"/>
-      <c r="S467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B468" s="2" t="n">
-        <v>46038</v>
+        <v>45523</v>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Norstat</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D468" t="n">
-        <v>1016</v>
+        <v>3443</v>
       </c>
       <c r="E468" t="b">
         <v>0</v>
       </c>
-      <c r="F468" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G468" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H468" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I468" t="n">
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
+      <c r="N468" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O468" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="P468" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R468" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="S468" t="n">
         <v>0.09</v>
       </c>
-      <c r="J468" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K468" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L468" t="inlineStr"/>
-      <c r="M468" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N468" t="inlineStr"/>
-      <c r="O468" t="inlineStr"/>
-      <c r="P468" t="inlineStr"/>
-      <c r="Q468" t="inlineStr"/>
-      <c r="R468" t="inlineStr"/>
-      <c r="S468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B469" s="2" t="n">
-        <v>46034</v>
+        <v>45477</v>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Survation</t>
+          <t>2024 general election</t>
         </is>
       </c>
       <c r="D469" t="n">
-        <v>1003</v>
+        <v>270</v>
       </c>
       <c r="E469" t="b">
         <v>0</v>
       </c>
-      <c r="F469" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G469" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H469" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I469" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J469" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="K469" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr"/>
       <c r="L469" t="inlineStr"/>
-      <c r="M469" t="n">
-        <v>0</v>
-      </c>
-      <c r="N469" t="inlineStr"/>
-      <c r="O469" t="inlineStr"/>
-      <c r="P469" t="inlineStr"/>
-      <c r="Q469" t="inlineStr"/>
-      <c r="R469" t="inlineStr"/>
-      <c r="S469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="O469" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P469" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="R469" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="S469" t="n">
+        <v>0.011</v>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B470" s="2" t="n">
-        <v>46010</v>
+        <v>45425</v>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Find Out Now</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D470" t="n">
-        <v>1000</v>
+        <v>1021</v>
       </c>
       <c r="E470" t="b">
         <v>0</v>
       </c>
-      <c r="F470" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G470" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H470" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I470" t="n">
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
+      <c r="N470" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O470" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="P470" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q470" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R470" t="n">
         <v>0.08</v>
       </c>
-      <c r="J470" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K470" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L470" t="inlineStr"/>
-      <c r="M470" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="N470" t="inlineStr"/>
-      <c r="O470" t="inlineStr"/>
-      <c r="P470" t="inlineStr"/>
-      <c r="Q470" t="inlineStr"/>
-      <c r="R470" t="inlineStr"/>
-      <c r="S470" t="inlineStr"/>
+      <c r="S470" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B471" s="2" t="n">
-        <v>45994</v>
+        <v>45334</v>
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D471" t="n">
-        <v>1055</v>
+        <v>3207</v>
       </c>
       <c r="E471" t="b">
         <v>0</v>
       </c>
-      <c r="F471" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G471" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H471" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I471" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J471" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="K471" t="n">
-        <v>0.33</v>
-      </c>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr"/>
       <c r="L471" t="inlineStr"/>
-      <c r="M471" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N471" t="inlineStr"/>
-      <c r="O471" t="inlineStr"/>
-      <c r="P471" t="inlineStr"/>
-      <c r="Q471" t="inlineStr"/>
-      <c r="R471" t="inlineStr"/>
-      <c r="S471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
+      <c r="N471" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O471" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P471" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Q471" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R471" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S471" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B472" s="2" t="n">
-        <v>45925</v>
+        <v>45229</v>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Norstat</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>1010</v>
+        <v>3046</v>
       </c>
       <c r="E472" t="b">
         <v>0</v>
       </c>
-      <c r="F472" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G472" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H472" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I472" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J472" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K472" t="n">
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="n">
         <v>0.31</v>
       </c>
-      <c r="L472" t="inlineStr"/>
-      <c r="M472" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N472" t="inlineStr"/>
-      <c r="O472" t="inlineStr"/>
-      <c r="P472" t="inlineStr"/>
-      <c r="Q472" t="inlineStr"/>
-      <c r="R472" t="inlineStr"/>
-      <c r="S472" t="inlineStr"/>
+      <c r="O472" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P472" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q472" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="R472" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="S472" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B473" s="2" t="n">
-        <v>45921</v>
+        <v>45152</v>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Find Out Now</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D473" t="n">
-        <v>1282</v>
+        <v>2950</v>
       </c>
       <c r="E473" t="b">
         <v>0</v>
       </c>
-      <c r="F473" t="n">
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O473" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P473" t="n">
         <v>0.15</v>
       </c>
-      <c r="G473" t="n">
+      <c r="Q473" t="n">
         <v>0.1</v>
       </c>
-      <c r="H473" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I473" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J473" t="n">
+      <c r="R473" t="n">
         <v>0.06</v>
       </c>
-      <c r="K473" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L473" t="inlineStr"/>
-      <c r="M473" t="n">
+      <c r="S473" t="n">
         <v>0.05</v>
       </c>
-      <c r="N473" t="inlineStr"/>
-      <c r="O473" t="inlineStr"/>
-      <c r="P473" t="inlineStr"/>
-      <c r="Q473" t="inlineStr"/>
-      <c r="R473" t="inlineStr"/>
-      <c r="S473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B474" s="2" t="n">
-        <v>45916</v>
+        <v>45064</v>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Survation</t>
+          <t>2023 local elections</t>
         </is>
       </c>
       <c r="D474" t="n">
-        <v>2051</v>
+        <v>309</v>
       </c>
       <c r="E474" t="b">
         <v>0</v>
       </c>
-      <c r="F474" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G474" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H474" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I474" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J474" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K474" t="n">
-        <v>0.35</v>
-      </c>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr"/>
       <c r="L474" t="inlineStr"/>
-      <c r="M474" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N474" t="inlineStr"/>
-      <c r="O474" t="inlineStr"/>
-      <c r="P474" t="inlineStr"/>
-      <c r="Q474" t="inlineStr"/>
-      <c r="R474" t="inlineStr"/>
-      <c r="S474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="O474" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="P474" t="n">
+        <v>0.109</v>
+      </c>
+      <c r="Q474" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="R474" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="S474" t="n">
+        <v>0.017</v>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B475" s="2" t="n">
-        <v>45901</v>
+        <v>45040</v>
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>More in Common</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D475" t="n">
-        <v>1104</v>
+        <v>3557</v>
       </c>
       <c r="E475" t="b">
         <v>0</v>
       </c>
-      <c r="F475" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="G475" t="n">
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O475" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P475" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q475" t="n">
         <v>0.11</v>
       </c>
-      <c r="H475" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I475" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J475" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K475" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L475" t="inlineStr"/>
-      <c r="M475" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N475" t="inlineStr"/>
-      <c r="O475" t="inlineStr"/>
-      <c r="P475" t="inlineStr"/>
-      <c r="Q475" t="inlineStr"/>
-      <c r="R475" t="inlineStr"/>
-      <c r="S475" t="inlineStr"/>
+      <c r="R475" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S475" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B476" s="2" t="n">
-        <v>45827</v>
+        <v>44999</v>
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>YouGov  [ failed verification ]</t>
+          <t>Institute of Irish Studies</t>
         </is>
       </c>
       <c r="D476" t="n">
-        <v>1178</v>
+        <v>1000</v>
       </c>
       <c r="E476" t="b">
         <v>0</v>
       </c>
-      <c r="F476" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G476" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H476" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I476" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J476" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K476" t="n">
-        <v>0.29</v>
-      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr"/>
       <c r="L476" t="inlineStr"/>
-      <c r="M476" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N476" t="inlineStr"/>
-      <c r="O476" t="inlineStr"/>
-      <c r="P476" t="inlineStr"/>
-      <c r="Q476" t="inlineStr"/>
-      <c r="R476" t="inlineStr"/>
-      <c r="S476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="O476" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="P476" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="Q476" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="R476" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="S476" t="n">
+        <v>0.048</v>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B477" s="2" t="n">
-        <v>45826</v>
+        <v>44949</v>
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Ipsos</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D477" t="n">
-        <v>1064</v>
+        <v>1499</v>
       </c>
       <c r="E477" t="b">
         <v>0</v>
       </c>
-      <c r="F477" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G477" t="n">
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O477" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P477" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q477" t="n">
         <v>0.1</v>
       </c>
-      <c r="H477" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I477" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J477" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K477" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L477" t="inlineStr"/>
-      <c r="M477" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N477" t="inlineStr"/>
-      <c r="O477" t="inlineStr"/>
-      <c r="P477" t="inlineStr"/>
-      <c r="Q477" t="inlineStr"/>
-      <c r="R477" t="inlineStr"/>
-      <c r="S477" t="inlineStr"/>
+      <c r="R477" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S477" t="n">
+        <v>0.07000000000000001</v>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B478" s="2" t="n">
-        <v>45807</v>
+        <v>44872</v>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Norstat</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D478" t="n">
-        <v>1007</v>
+        <v>3351</v>
       </c>
       <c r="E478" t="b">
         <v>0</v>
       </c>
-      <c r="F478" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G478" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H478" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I478" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J478" t="n">
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="O478" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P478" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Q478" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="R478" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="K478" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L478" t="inlineStr"/>
-      <c r="M478" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N478" t="inlineStr"/>
-      <c r="O478" t="inlineStr"/>
-      <c r="P478" t="inlineStr"/>
-      <c r="Q478" t="inlineStr"/>
-      <c r="R478" t="inlineStr"/>
-      <c r="S478" t="inlineStr"/>
+      <c r="S478" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B479" s="2" t="n">
-        <v>45782</v>
+        <v>44788</v>
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Survation</t>
+          <t>LucidTalk</t>
         </is>
       </c>
       <c r="D479" t="n">
-        <v>1020</v>
+        <v>3384</v>
       </c>
       <c r="E479" t="b">
         <v>0</v>
       </c>
-      <c r="F479" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G479" t="n">
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="O479" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P479" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="Q479" t="n">
         <v>0.11</v>
       </c>
-      <c r="H479" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I479" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J479" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K479" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L479" t="inlineStr"/>
-      <c r="M479" t="n">
-        <v>0</v>
-      </c>
-      <c r="N479" t="inlineStr"/>
-      <c r="O479" t="inlineStr"/>
-      <c r="P479" t="inlineStr"/>
-      <c r="Q479" t="inlineStr"/>
-      <c r="R479" t="inlineStr"/>
-      <c r="S479" t="inlineStr"/>
+      <c r="R479" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="S479" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B480" s="2" t="n">
-        <v>45769</v>
+        <v>44752</v>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Survation</t>
+          <t>Institute of Irish Studies</t>
         </is>
       </c>
       <c r="D480" t="n">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="E480" t="b">
         <v>0</v>
       </c>
-      <c r="F480" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G480" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H480" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I480" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J480" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K480" t="n">
-        <v>0.33</v>
-      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr"/>
       <c r="L480" t="inlineStr"/>
-      <c r="M480" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N480" t="inlineStr"/>
-      <c r="O480" t="inlineStr"/>
-      <c r="P480" t="inlineStr"/>
-      <c r="Q480" t="inlineStr"/>
-      <c r="R480" t="inlineStr"/>
-      <c r="S480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="O480" t="n">
+        <v>0.201</v>
+      </c>
+      <c r="P480" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="Q480" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="R480" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="S480" t="n">
+        <v>0.047</v>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>NI</t>
         </is>
       </c>
       <c r="B481" s="2" t="n">
-        <v>45719</v>
+        <v>44686</v>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>YouGov  [ failed verification ]</t>
+          <t>2022 Assembly election</t>
         </is>
       </c>
       <c r="D481" t="n">
-        <v>1164</v>
+        <v>290</v>
       </c>
       <c r="E481" t="b">
         <v>0</v>
       </c>
-      <c r="F481" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G481" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H481" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I481" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J481" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K481" t="n">
-        <v>0.32</v>
-      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr"/>
-      <c r="M481" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N481" t="inlineStr"/>
-      <c r="O481" t="inlineStr"/>
-      <c r="P481" t="inlineStr"/>
-      <c r="Q481" t="inlineStr"/>
-      <c r="R481" t="inlineStr"/>
-      <c r="S481" t="inlineStr"/>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B482" s="2" t="n">
-        <v>45677</v>
-      </c>
-      <c r="C482" t="inlineStr">
-        <is>
-          <t>Find Out Now</t>
-        </is>
-      </c>
-      <c r="D482" t="n">
-        <v>1334</v>
-      </c>
-      <c r="E482" t="b">
-        <v>0</v>
-      </c>
-      <c r="F482" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G482" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H482" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I482" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J482" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K482" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L482" t="inlineStr"/>
-      <c r="M482" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N482" t="inlineStr"/>
-      <c r="O482" t="inlineStr"/>
-      <c r="P482" t="inlineStr"/>
-      <c r="Q482" t="inlineStr"/>
-      <c r="R482" t="inlineStr"/>
-      <c r="S482" t="inlineStr"/>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B483" s="2" t="n">
-        <v>45671</v>
-      </c>
-      <c r="C483" t="inlineStr">
-        <is>
-          <t>Norstat</t>
-        </is>
-      </c>
-      <c r="D483" t="n">
-        <v>1026</v>
-      </c>
-      <c r="E483" t="b">
-        <v>0</v>
-      </c>
-      <c r="F483" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G483" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H483" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I483" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J483" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K483" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L483" t="inlineStr"/>
-      <c r="M483" t="n">
-        <v>0</v>
-      </c>
-      <c r="N483" t="inlineStr"/>
-      <c r="O483" t="inlineStr"/>
-      <c r="P483" t="inlineStr"/>
-      <c r="Q483" t="inlineStr"/>
-      <c r="R483" t="inlineStr"/>
-      <c r="S483" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B484" s="2" t="n">
-        <v>45670</v>
-      </c>
-      <c r="C484" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D484" t="n">
-        <v>1024</v>
-      </c>
-      <c r="E484" t="b">
-        <v>0</v>
-      </c>
-      <c r="F484" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G484" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H484" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I484" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J484" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K484" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="L484" t="inlineStr"/>
-      <c r="M484" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N484" t="inlineStr"/>
-      <c r="O484" t="inlineStr"/>
-      <c r="P484" t="inlineStr"/>
-      <c r="Q484" t="inlineStr"/>
-      <c r="R484" t="inlineStr"/>
-      <c r="S484" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B485" s="2" t="n">
-        <v>45650</v>
-      </c>
-      <c r="C485" t="inlineStr">
-        <is>
-          <t>Find Out Now</t>
-        </is>
-      </c>
-      <c r="D485" t="n">
-        <v>1774</v>
-      </c>
-      <c r="E485" t="b">
-        <v>0</v>
-      </c>
-      <c r="F485" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G485" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H485" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I485" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J485" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K485" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="L485" t="inlineStr"/>
-      <c r="M485" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N485" t="inlineStr"/>
-      <c r="O485" t="inlineStr"/>
-      <c r="P485" t="inlineStr"/>
-      <c r="Q485" t="inlineStr"/>
-      <c r="R485" t="inlineStr"/>
-      <c r="S485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B486" s="2" t="n">
-        <v>45632</v>
-      </c>
-      <c r="C486" t="inlineStr">
-        <is>
-          <t>Norstat</t>
-        </is>
-      </c>
-      <c r="D486" t="n">
-        <v>1013</v>
-      </c>
-      <c r="E486" t="b">
-        <v>0</v>
-      </c>
-      <c r="F486" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G486" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H486" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I486" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J486" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K486" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L486" t="inlineStr"/>
-      <c r="M486" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N486" t="inlineStr"/>
-      <c r="O486" t="inlineStr"/>
-      <c r="P486" t="inlineStr"/>
-      <c r="Q486" t="inlineStr"/>
-      <c r="R486" t="inlineStr"/>
-      <c r="S486" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B487" s="2" t="n">
-        <v>45611</v>
-      </c>
-      <c r="C487" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D487" t="n">
-        <v>3016</v>
-      </c>
-      <c r="E487" t="b">
-        <v>0</v>
-      </c>
-      <c r="F487" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="G487" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H487" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I487" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J487" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K487" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L487" t="inlineStr"/>
-      <c r="M487" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N487" t="inlineStr"/>
-      <c r="O487" t="inlineStr"/>
-      <c r="P487" t="inlineStr"/>
-      <c r="Q487" t="inlineStr"/>
-      <c r="R487" t="inlineStr"/>
-      <c r="S487" t="inlineStr"/>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B488" s="2" t="n">
-        <v>45597</v>
-      </c>
-      <c r="C488" t="inlineStr">
-        <is>
-          <t>Norstat</t>
-        </is>
-      </c>
-      <c r="D488" t="n">
-        <v>1013</v>
-      </c>
-      <c r="E488" t="b">
-        <v>0</v>
-      </c>
-      <c r="F488" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G488" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H488" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I488" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J488" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K488" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L488" t="inlineStr"/>
-      <c r="M488" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N488" t="inlineStr"/>
-      <c r="O488" t="inlineStr"/>
-      <c r="P488" t="inlineStr"/>
-      <c r="Q488" t="inlineStr"/>
-      <c r="R488" t="inlineStr"/>
-      <c r="S488" t="inlineStr"/>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B489" s="2" t="n">
-        <v>45548</v>
-      </c>
-      <c r="C489" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D489" t="n">
-        <v>2059</v>
-      </c>
-      <c r="E489" t="b">
-        <v>0</v>
-      </c>
-      <c r="F489" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="G489" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H489" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I489" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J489" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="K489" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="L489" t="inlineStr"/>
-      <c r="M489" t="n">
-        <v>0</v>
-      </c>
-      <c r="N489" t="inlineStr"/>
-      <c r="O489" t="inlineStr"/>
-      <c r="P489" t="inlineStr"/>
-      <c r="Q489" t="inlineStr"/>
-      <c r="R489" t="inlineStr"/>
-      <c r="S489" t="inlineStr"/>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B490" s="2" t="n">
-        <v>45546</v>
-      </c>
-      <c r="C490" t="inlineStr">
-        <is>
-          <t>Opinium</t>
-        </is>
-      </c>
-      <c r="D490" t="n">
-        <v>1028</v>
-      </c>
-      <c r="E490" t="b">
-        <v>0</v>
-      </c>
-      <c r="F490" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G490" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H490" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I490" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J490" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K490" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="L490" t="inlineStr"/>
-      <c r="M490" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N490" t="inlineStr"/>
-      <c r="O490" t="inlineStr"/>
-      <c r="P490" t="inlineStr"/>
-      <c r="Q490" t="inlineStr"/>
-      <c r="R490" t="inlineStr"/>
-      <c r="S490" t="inlineStr"/>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B491" s="2" t="n">
-        <v>45526</v>
-      </c>
-      <c r="C491" t="inlineStr">
-        <is>
-          <t>Norstat</t>
-        </is>
-      </c>
-      <c r="D491" t="n">
-        <v>1011</v>
-      </c>
-      <c r="E491" t="b">
-        <v>0</v>
-      </c>
-      <c r="F491" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G491" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H491" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I491" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J491" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K491" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="L491" t="inlineStr"/>
-      <c r="M491" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N491" t="inlineStr"/>
-      <c r="O491" t="inlineStr"/>
-      <c r="P491" t="inlineStr"/>
-      <c r="Q491" t="inlineStr"/>
-      <c r="R491" t="inlineStr"/>
-      <c r="S491" t="inlineStr"/>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B492" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C492" t="inlineStr">
-        <is>
-          <t>2024 general election</t>
-        </is>
-      </c>
-      <c r="D492" t="n">
-        <v>353</v>
-      </c>
-      <c r="E492" t="b">
-        <v>0</v>
-      </c>
-      <c r="F492" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G492" t="n">
-        <v>0.09699999999999999</v>
-      </c>
-      <c r="H492" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="I492" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="J492" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="K492" t="n">
-        <v>0.127</v>
-      </c>
-      <c r="L492" t="inlineStr"/>
-      <c r="M492" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="N492" t="inlineStr"/>
-      <c r="O492" t="inlineStr"/>
-      <c r="P492" t="inlineStr"/>
-      <c r="Q492" t="inlineStr"/>
-      <c r="R492" t="inlineStr"/>
-      <c r="S492" t="inlineStr"/>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B493" s="2" t="n">
-        <v>46100</v>
-      </c>
-      <c r="C493" t="inlineStr">
-        <is>
-          <t>YouGov</t>
-        </is>
-      </c>
-      <c r="D493" t="n">
-        <v>1082</v>
-      </c>
-      <c r="E493" t="b">
-        <v>0</v>
-      </c>
-      <c r="F493" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G493" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H493" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I493" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="J493" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K493" t="inlineStr"/>
-      <c r="L493" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M493" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N493" t="inlineStr"/>
-      <c r="O493" t="inlineStr"/>
-      <c r="P493" t="inlineStr"/>
-      <c r="Q493" t="inlineStr"/>
-      <c r="R493" t="inlineStr"/>
-      <c r="S493" t="inlineStr"/>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B494" s="2" t="n">
-        <v>46034</v>
-      </c>
-      <c r="C494" t="inlineStr">
-        <is>
-          <t>YouGov</t>
-        </is>
-      </c>
-      <c r="D494" t="n">
-        <v>1205</v>
-      </c>
-      <c r="E494" t="b">
-        <v>0</v>
-      </c>
-      <c r="F494" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="G494" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H494" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I494" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J494" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K494" t="inlineStr"/>
-      <c r="L494" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M494" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N494" t="inlineStr"/>
-      <c r="O494" t="inlineStr"/>
-      <c r="P494" t="inlineStr"/>
-      <c r="Q494" t="inlineStr"/>
-      <c r="R494" t="inlineStr"/>
-      <c r="S494" t="inlineStr"/>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B495" s="2" t="n">
-        <v>46001</v>
-      </c>
-      <c r="C495" t="inlineStr">
-        <is>
-          <t>YouGov</t>
-        </is>
-      </c>
-      <c r="D495" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E495" t="b">
-        <v>0</v>
-      </c>
-      <c r="F495" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G495" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H495" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I495" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J495" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="K495" t="inlineStr"/>
-      <c r="L495" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="M495" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N495" t="inlineStr"/>
-      <c r="O495" t="inlineStr"/>
-      <c r="P495" t="inlineStr"/>
-      <c r="Q495" t="inlineStr"/>
-      <c r="R495" t="inlineStr"/>
-      <c r="S495" t="inlineStr"/>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B496" s="2" t="n">
-        <v>45910</v>
-      </c>
-      <c r="C496" t="inlineStr">
-        <is>
-          <t>YouGov</t>
-        </is>
-      </c>
-      <c r="D496" t="n">
-        <v>1220</v>
-      </c>
-      <c r="E496" t="b">
-        <v>0</v>
-      </c>
-      <c r="F496" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="G496" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H496" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="I496" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J496" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K496" t="inlineStr"/>
-      <c r="L496" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="M496" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N496" t="inlineStr"/>
-      <c r="O496" t="inlineStr"/>
-      <c r="P496" t="inlineStr"/>
-      <c r="Q496" t="inlineStr"/>
-      <c r="R496" t="inlineStr"/>
-      <c r="S496" t="inlineStr"/>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B497" s="2" t="n">
-        <v>45777</v>
-      </c>
-      <c r="C497" t="inlineStr">
-        <is>
-          <t>YouGov</t>
-        </is>
-      </c>
-      <c r="D497" t="n">
-        <v>1248</v>
-      </c>
-      <c r="E497" t="b">
-        <v>0</v>
-      </c>
-      <c r="F497" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G497" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="H497" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="I497" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J497" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K497" t="inlineStr"/>
-      <c r="L497" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="M497" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N497" t="inlineStr"/>
-      <c r="O497" t="inlineStr"/>
-      <c r="P497" t="inlineStr"/>
-      <c r="Q497" t="inlineStr"/>
-      <c r="R497" t="inlineStr"/>
-      <c r="S497" t="inlineStr"/>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B498" s="2" t="n">
-        <v>45750</v>
-      </c>
-      <c r="C498" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D498" t="n">
-        <v>844</v>
-      </c>
-      <c r="E498" t="b">
-        <v>0</v>
-      </c>
-      <c r="F498" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="G498" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="H498" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I498" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J498" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K498" t="inlineStr"/>
-      <c r="L498" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M498" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N498" t="inlineStr"/>
-      <c r="O498" t="inlineStr"/>
-      <c r="P498" t="inlineStr"/>
-      <c r="Q498" t="inlineStr"/>
-      <c r="R498" t="inlineStr"/>
-      <c r="S498" t="inlineStr"/>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B499" s="2" t="n">
-        <v>45600</v>
-      </c>
-      <c r="C499" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D499" t="n">
-        <v>2006</v>
-      </c>
-      <c r="E499" t="b">
-        <v>0</v>
-      </c>
-      <c r="F499" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G499" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H499" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I499" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="J499" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K499" t="inlineStr"/>
-      <c r="L499" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="M499" t="n">
-        <v>0</v>
-      </c>
-      <c r="N499" t="inlineStr"/>
-      <c r="O499" t="inlineStr"/>
-      <c r="P499" t="inlineStr"/>
-      <c r="Q499" t="inlineStr"/>
-      <c r="R499" t="inlineStr"/>
-      <c r="S499" t="inlineStr"/>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B500" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C500" t="inlineStr">
-        <is>
-          <t>2024 general election</t>
-        </is>
-      </c>
-      <c r="D500" t="n">
-        <v>370</v>
-      </c>
-      <c r="E500" t="b">
-        <v>0</v>
-      </c>
-      <c r="F500" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="G500" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="H500" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="I500" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="J500" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="K500" t="inlineStr"/>
-      <c r="L500" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="M500" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="N500" t="inlineStr"/>
-      <c r="O500" t="inlineStr"/>
-      <c r="P500" t="inlineStr"/>
-      <c r="Q500" t="inlineStr"/>
-      <c r="R500" t="inlineStr"/>
-      <c r="S500" t="inlineStr"/>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B501" s="2" t="n">
-        <v>45617</v>
-      </c>
-      <c r="C501" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D501" t="n">
-        <v>1007</v>
-      </c>
-      <c r="E501" t="b">
-        <v>0</v>
-      </c>
-      <c r="F501" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G501" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H501" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I501" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J501" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="K501" t="inlineStr"/>
-      <c r="L501" t="inlineStr"/>
-      <c r="M501" t="n">
-        <v>0</v>
-      </c>
-      <c r="N501" t="inlineStr"/>
-      <c r="O501" t="inlineStr"/>
-      <c r="P501" t="inlineStr"/>
-      <c r="Q501" t="inlineStr"/>
-      <c r="R501" t="inlineStr"/>
-      <c r="S501" t="inlineStr"/>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B502" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C502" t="inlineStr">
-        <is>
-          <t>2024 general election (Survation)</t>
-        </is>
-      </c>
-      <c r="D502" t="n">
-        <v>339</v>
-      </c>
-      <c r="E502" t="b">
-        <v>0</v>
-      </c>
-      <c r="F502" t="n">
-        <v>0.191</v>
-      </c>
-      <c r="G502" t="n">
-        <v>0.236</v>
-      </c>
-      <c r="H502" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I502" t="n">
-        <v>0.161</v>
-      </c>
-      <c r="J502" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="K502" t="inlineStr"/>
-      <c r="L502" t="inlineStr"/>
-      <c r="M502" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="N502" t="inlineStr"/>
-      <c r="O502" t="inlineStr"/>
-      <c r="P502" t="inlineStr"/>
-      <c r="Q502" t="inlineStr"/>
-      <c r="R502" t="inlineStr"/>
-      <c r="S502" t="inlineStr"/>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B503" s="2" t="n">
-        <v>45760</v>
-      </c>
-      <c r="C503" t="inlineStr">
-        <is>
-          <t>Survation</t>
-        </is>
-      </c>
-      <c r="D503" t="n">
-        <v>2032</v>
-      </c>
-      <c r="E503" t="b">
-        <v>0</v>
-      </c>
-      <c r="F503" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G503" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="H503" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I503" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J503" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K503" t="inlineStr"/>
-      <c r="L503" t="inlineStr"/>
-      <c r="M503" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N503" t="inlineStr"/>
-      <c r="O503" t="inlineStr"/>
-      <c r="P503" t="inlineStr"/>
-      <c r="Q503" t="inlineStr"/>
-      <c r="R503" t="inlineStr"/>
-      <c r="S503" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B504" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C504" t="inlineStr">
-        <is>
-          <t>2024 general election</t>
-        </is>
-      </c>
-      <c r="D504" t="n">
-        <v>396</v>
-      </c>
-      <c r="E504" t="b">
-        <v>0</v>
-      </c>
-      <c r="F504" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="G504" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="H504" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I504" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="J504" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="K504" t="inlineStr"/>
-      <c r="L504" t="inlineStr"/>
-      <c r="M504" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="N504" t="inlineStr"/>
-      <c r="O504" t="inlineStr"/>
-      <c r="P504" t="inlineStr"/>
-      <c r="Q504" t="inlineStr"/>
-      <c r="R504" t="inlineStr"/>
-      <c r="S504" t="inlineStr"/>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B505" s="2" t="n">
-        <v>46014</v>
-      </c>
-      <c r="C505" t="inlineStr">
-        <is>
-          <t>Savanta</t>
-        </is>
-      </c>
-      <c r="D505" t="n">
-        <v>1006</v>
-      </c>
-      <c r="E505" t="b">
-        <v>0</v>
-      </c>
-      <c r="F505" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G505" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H505" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="I505" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J505" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="K505" t="inlineStr"/>
-      <c r="L505" t="inlineStr"/>
-      <c r="M505" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N505" t="inlineStr"/>
-      <c r="O505" t="inlineStr"/>
-      <c r="P505" t="inlineStr"/>
-      <c r="Q505" t="inlineStr"/>
-      <c r="R505" t="inlineStr"/>
-      <c r="S505" t="inlineStr"/>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B506" s="2" t="n">
-        <v>46012</v>
-      </c>
-      <c r="C506" t="inlineStr">
-        <is>
-          <t>Savanta</t>
-        </is>
-      </c>
-      <c r="D506" t="n">
-        <v>1006</v>
-      </c>
-      <c r="E506" t="b">
-        <v>0</v>
-      </c>
-      <c r="F506" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="G506" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H506" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I506" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J506" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K506" t="inlineStr"/>
-      <c r="L506" t="inlineStr"/>
-      <c r="M506" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="N506" t="inlineStr"/>
-      <c r="O506" t="inlineStr"/>
-      <c r="P506" t="inlineStr"/>
-      <c r="Q506" t="inlineStr"/>
-      <c r="R506" t="inlineStr"/>
-      <c r="S506" t="inlineStr"/>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B507" s="2" t="n">
-        <v>45968</v>
-      </c>
-      <c r="C507" t="inlineStr">
-        <is>
-          <t>Savanta</t>
-        </is>
-      </c>
-      <c r="D507" t="n">
-        <v>1242</v>
-      </c>
-      <c r="E507" t="b">
-        <v>0</v>
-      </c>
-      <c r="F507" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G507" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H507" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="I507" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="J507" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K507" t="inlineStr"/>
-      <c r="L507" t="inlineStr"/>
-      <c r="M507" t="inlineStr"/>
-      <c r="N507" t="inlineStr"/>
-      <c r="O507" t="inlineStr"/>
-      <c r="P507" t="inlineStr"/>
-      <c r="Q507" t="inlineStr"/>
-      <c r="R507" t="inlineStr"/>
-      <c r="S507" t="inlineStr"/>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B508" s="2" t="n">
-        <v>45798</v>
-      </c>
-      <c r="C508" t="inlineStr">
-        <is>
-          <t>Savanta</t>
-        </is>
-      </c>
-      <c r="D508" t="n">
-        <v>1003</v>
-      </c>
-      <c r="E508" t="b">
-        <v>0</v>
-      </c>
-      <c r="F508" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="G508" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H508" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I508" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="J508" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="K508" t="inlineStr"/>
-      <c r="L508" t="inlineStr"/>
-      <c r="M508" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N508" t="inlineStr"/>
-      <c r="O508" t="inlineStr"/>
-      <c r="P508" t="inlineStr"/>
-      <c r="Q508" t="inlineStr"/>
-      <c r="R508" t="inlineStr"/>
-      <c r="S508" t="inlineStr"/>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B509" s="2" t="n">
-        <v>45785</v>
-      </c>
-      <c r="C509" t="inlineStr">
-        <is>
-          <t>Find Out Now</t>
-        </is>
-      </c>
-      <c r="D509" t="n">
-        <v>1102</v>
-      </c>
-      <c r="E509" t="b">
-        <v>0</v>
-      </c>
-      <c r="F509" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G509" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H509" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="I509" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J509" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K509" t="inlineStr"/>
-      <c r="L509" t="inlineStr"/>
-      <c r="M509" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N509" t="inlineStr"/>
-      <c r="O509" t="inlineStr"/>
-      <c r="P509" t="inlineStr"/>
-      <c r="Q509" t="inlineStr"/>
-      <c r="R509" t="inlineStr"/>
-      <c r="S509" t="inlineStr"/>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B510" s="2" t="n">
-        <v>45607</v>
-      </c>
-      <c r="C510" t="inlineStr">
-        <is>
-          <t>Savanta</t>
-        </is>
-      </c>
-      <c r="D510" t="n">
-        <v>1004</v>
-      </c>
-      <c r="E510" t="b">
-        <v>0</v>
-      </c>
-      <c r="F510" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="G510" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H510" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I510" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J510" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="K510" t="inlineStr"/>
-      <c r="L510" t="inlineStr"/>
-      <c r="M510" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N510" t="inlineStr"/>
-      <c r="O510" t="inlineStr"/>
-      <c r="P510" t="inlineStr"/>
-      <c r="Q510" t="inlineStr"/>
-      <c r="R510" t="inlineStr"/>
-      <c r="S510" t="inlineStr"/>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B511" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C511" t="inlineStr">
-        <is>
-          <t>2024 general election</t>
-        </is>
-      </c>
-      <c r="D511" t="n">
-        <v>430</v>
-      </c>
-      <c r="E511" t="b">
-        <v>0</v>
-      </c>
-      <c r="F511" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="G511" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="H511" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="I511" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J511" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="K511" t="inlineStr"/>
-      <c r="L511" t="inlineStr"/>
-      <c r="M511" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="N511" t="inlineStr"/>
-      <c r="O511" t="inlineStr"/>
-      <c r="P511" t="inlineStr"/>
-      <c r="Q511" t="inlineStr"/>
-      <c r="R511" t="inlineStr"/>
-      <c r="S511" t="inlineStr"/>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B512" s="2" t="n">
-        <v>46046</v>
-      </c>
-      <c r="C512" t="inlineStr">
-        <is>
-          <t>Find Out Now</t>
-        </is>
-      </c>
-      <c r="D512" t="n">
-        <v>1003</v>
-      </c>
-      <c r="E512" t="b">
-        <v>0</v>
-      </c>
-      <c r="F512" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="G512" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H512" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="I512" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="J512" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K512" t="inlineStr"/>
-      <c r="L512" t="inlineStr"/>
-      <c r="M512" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="N512" t="inlineStr"/>
-      <c r="O512" t="inlineStr"/>
-      <c r="P512" t="inlineStr"/>
-      <c r="Q512" t="inlineStr"/>
-      <c r="R512" t="inlineStr"/>
-      <c r="S512" t="inlineStr"/>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="B513" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C513" t="inlineStr">
-        <is>
-          <t>2024 general election</t>
-        </is>
-      </c>
-      <c r="D513" t="n">
-        <v>430</v>
-      </c>
-      <c r="E513" t="b">
-        <v>0</v>
-      </c>
-      <c r="F513" t="n">
-        <v>0.174</v>
-      </c>
-      <c r="G513" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H513" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="I513" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="J513" t="n">
-        <v>0.068</v>
-      </c>
-      <c r="K513" t="inlineStr"/>
-      <c r="L513" t="inlineStr"/>
-      <c r="M513" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="N513" t="inlineStr"/>
-      <c r="O513" t="inlineStr"/>
-      <c r="P513" t="inlineStr"/>
-      <c r="Q513" t="inlineStr"/>
-      <c r="R513" t="inlineStr"/>
-      <c r="S513" t="inlineStr"/>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B514" s="2" t="n">
-        <v>46124</v>
-      </c>
-      <c r="C514" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D514" t="n">
-        <v>3162</v>
-      </c>
-      <c r="E514" t="b">
-        <v>0</v>
-      </c>
-      <c r="F514" t="inlineStr"/>
-      <c r="G514" t="inlineStr"/>
-      <c r="H514" t="inlineStr"/>
-      <c r="I514" t="inlineStr"/>
-      <c r="J514" t="inlineStr"/>
-      <c r="K514" t="inlineStr"/>
-      <c r="L514" t="inlineStr"/>
-      <c r="M514" t="inlineStr"/>
-      <c r="N514" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="O514" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="P514" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q514" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="R514" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="S514" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B515" s="2" t="n">
-        <v>46041</v>
-      </c>
-      <c r="C515" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D515" t="n">
-        <v>2975</v>
-      </c>
-      <c r="E515" t="b">
-        <v>0</v>
-      </c>
-      <c r="F515" t="inlineStr"/>
-      <c r="G515" t="inlineStr"/>
-      <c r="H515" t="inlineStr"/>
-      <c r="I515" t="inlineStr"/>
-      <c r="J515" t="inlineStr"/>
-      <c r="K515" t="inlineStr"/>
-      <c r="L515" t="inlineStr"/>
-      <c r="M515" t="inlineStr"/>
-      <c r="N515" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O515" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="P515" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q515" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="R515" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="S515" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B516" s="2" t="n">
-        <v>45950</v>
-      </c>
-      <c r="C516" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D516" t="n">
-        <v>2908</v>
-      </c>
-      <c r="E516" t="b">
-        <v>0</v>
-      </c>
-      <c r="F516" t="inlineStr"/>
-      <c r="G516" t="inlineStr"/>
-      <c r="H516" t="inlineStr"/>
-      <c r="I516" t="inlineStr"/>
-      <c r="J516" t="inlineStr"/>
-      <c r="K516" t="inlineStr"/>
-      <c r="L516" t="inlineStr"/>
-      <c r="M516" t="inlineStr"/>
-      <c r="N516" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O516" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="P516" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Q516" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R516" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="S516" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B517" s="2" t="n">
-        <v>45880</v>
-      </c>
-      <c r="C517" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D517" t="n">
-        <v>3028</v>
-      </c>
-      <c r="E517" t="b">
-        <v>0</v>
-      </c>
-      <c r="F517" t="inlineStr"/>
-      <c r="G517" t="inlineStr"/>
-      <c r="H517" t="inlineStr"/>
-      <c r="I517" t="inlineStr"/>
-      <c r="J517" t="inlineStr"/>
-      <c r="K517" t="inlineStr"/>
-      <c r="L517" t="inlineStr"/>
-      <c r="M517" t="inlineStr"/>
-      <c r="N517" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="O517" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="P517" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Q517" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R517" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="S517" t="n">
-        <v>0.13</v>
-      </c>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B518" s="2" t="n">
-        <v>45796</v>
-      </c>
-      <c r="C518" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D518" t="n">
-        <v>2755</v>
-      </c>
-      <c r="E518" t="b">
-        <v>0</v>
-      </c>
-      <c r="F518" t="inlineStr"/>
-      <c r="G518" t="inlineStr"/>
-      <c r="H518" t="inlineStr"/>
-      <c r="I518" t="inlineStr"/>
-      <c r="J518" t="inlineStr"/>
-      <c r="K518" t="inlineStr"/>
-      <c r="L518" t="inlineStr"/>
-      <c r="M518" t="inlineStr"/>
-      <c r="N518" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="O518" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="P518" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q518" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R518" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="S518" t="n">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B519" s="2" t="n">
-        <v>45705</v>
-      </c>
-      <c r="C519" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D519" t="n">
-        <v>3001</v>
-      </c>
-      <c r="E519" t="b">
-        <v>0</v>
-      </c>
-      <c r="F519" t="inlineStr"/>
-      <c r="G519" t="inlineStr"/>
-      <c r="H519" t="inlineStr"/>
-      <c r="I519" t="inlineStr"/>
-      <c r="J519" t="inlineStr"/>
-      <c r="K519" t="inlineStr"/>
-      <c r="L519" t="inlineStr"/>
-      <c r="M519" t="inlineStr"/>
-      <c r="N519" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O519" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="P519" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Q519" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R519" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="S519" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B520" s="2" t="n">
-        <v>45600</v>
-      </c>
-      <c r="C520" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D520" t="n">
-        <v>3209</v>
-      </c>
-      <c r="E520" t="b">
-        <v>0</v>
-      </c>
-      <c r="F520" t="inlineStr"/>
-      <c r="G520" t="inlineStr"/>
-      <c r="H520" t="inlineStr"/>
-      <c r="I520" t="inlineStr"/>
-      <c r="J520" t="inlineStr"/>
-      <c r="K520" t="inlineStr"/>
-      <c r="L520" t="inlineStr"/>
-      <c r="M520" t="inlineStr"/>
-      <c r="N520" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O520" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="P520" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q520" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R520" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S520" t="n">
-        <v>0.11</v>
-      </c>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B521" s="2" t="n">
-        <v>45523</v>
-      </c>
-      <c r="C521" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D521" t="n">
-        <v>3443</v>
-      </c>
-      <c r="E521" t="b">
-        <v>0</v>
-      </c>
-      <c r="F521" t="inlineStr"/>
-      <c r="G521" t="inlineStr"/>
-      <c r="H521" t="inlineStr"/>
-      <c r="I521" t="inlineStr"/>
-      <c r="J521" t="inlineStr"/>
-      <c r="K521" t="inlineStr"/>
-      <c r="L521" t="inlineStr"/>
-      <c r="M521" t="inlineStr"/>
-      <c r="N521" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O521" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="P521" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q521" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R521" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="S521" t="n">
-        <v>0.09</v>
-      </c>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B522" s="2" t="n">
-        <v>45477</v>
-      </c>
-      <c r="C522" t="inlineStr">
-        <is>
-          <t>2024 general election</t>
-        </is>
-      </c>
-      <c r="D522" t="n">
-        <v>270</v>
-      </c>
-      <c r="E522" t="b">
-        <v>0</v>
-      </c>
-      <c r="F522" t="inlineStr"/>
-      <c r="G522" t="inlineStr"/>
-      <c r="H522" t="inlineStr"/>
-      <c r="I522" t="inlineStr"/>
-      <c r="J522" t="inlineStr"/>
-      <c r="K522" t="inlineStr"/>
-      <c r="L522" t="inlineStr"/>
-      <c r="M522" t="inlineStr"/>
-      <c r="N522" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="O522" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="P522" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="Q522" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="R522" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="S522" t="n">
-        <v>0.011</v>
-      </c>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B523" s="2" t="n">
-        <v>45425</v>
-      </c>
-      <c r="C523" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D523" t="n">
-        <v>1021</v>
-      </c>
-      <c r="E523" t="b">
-        <v>0</v>
-      </c>
-      <c r="F523" t="inlineStr"/>
-      <c r="G523" t="inlineStr"/>
-      <c r="H523" t="inlineStr"/>
-      <c r="I523" t="inlineStr"/>
-      <c r="J523" t="inlineStr"/>
-      <c r="K523" t="inlineStr"/>
-      <c r="L523" t="inlineStr"/>
-      <c r="M523" t="inlineStr"/>
-      <c r="N523" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O523" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="P523" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q523" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R523" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="S523" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B524" s="2" t="n">
-        <v>45334</v>
-      </c>
-      <c r="C524" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D524" t="n">
-        <v>3207</v>
-      </c>
-      <c r="E524" t="b">
-        <v>0</v>
-      </c>
-      <c r="F524" t="inlineStr"/>
-      <c r="G524" t="inlineStr"/>
-      <c r="H524" t="inlineStr"/>
-      <c r="I524" t="inlineStr"/>
-      <c r="J524" t="inlineStr"/>
-      <c r="K524" t="inlineStr"/>
-      <c r="L524" t="inlineStr"/>
-      <c r="M524" t="inlineStr"/>
-      <c r="N524" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O524" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="P524" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Q524" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R524" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S524" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B525" s="2" t="n">
-        <v>45229</v>
-      </c>
-      <c r="C525" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D525" t="n">
-        <v>3046</v>
-      </c>
-      <c r="E525" t="b">
-        <v>0</v>
-      </c>
-      <c r="F525" t="inlineStr"/>
-      <c r="G525" t="inlineStr"/>
-      <c r="H525" t="inlineStr"/>
-      <c r="I525" t="inlineStr"/>
-      <c r="J525" t="inlineStr"/>
-      <c r="K525" t="inlineStr"/>
-      <c r="L525" t="inlineStr"/>
-      <c r="M525" t="inlineStr"/>
-      <c r="N525" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O525" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="P525" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q525" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="R525" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S525" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B526" s="2" t="n">
-        <v>45152</v>
-      </c>
-      <c r="C526" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D526" t="n">
-        <v>2950</v>
-      </c>
-      <c r="E526" t="b">
-        <v>0</v>
-      </c>
-      <c r="F526" t="inlineStr"/>
-      <c r="G526" t="inlineStr"/>
-      <c r="H526" t="inlineStr"/>
-      <c r="I526" t="inlineStr"/>
-      <c r="J526" t="inlineStr"/>
-      <c r="K526" t="inlineStr"/>
-      <c r="L526" t="inlineStr"/>
-      <c r="M526" t="inlineStr"/>
-      <c r="N526" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O526" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="P526" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q526" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R526" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="S526" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B527" s="2" t="n">
-        <v>45064</v>
-      </c>
-      <c r="C527" t="inlineStr">
-        <is>
-          <t>2023 local elections</t>
-        </is>
-      </c>
-      <c r="D527" t="n">
-        <v>309</v>
-      </c>
-      <c r="E527" t="b">
-        <v>0</v>
-      </c>
-      <c r="F527" t="inlineStr"/>
-      <c r="G527" t="inlineStr"/>
-      <c r="H527" t="inlineStr"/>
-      <c r="I527" t="inlineStr"/>
-      <c r="J527" t="inlineStr"/>
-      <c r="K527" t="inlineStr"/>
-      <c r="L527" t="inlineStr"/>
-      <c r="M527" t="inlineStr"/>
-      <c r="N527" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="O527" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="P527" t="n">
-        <v>0.109</v>
-      </c>
-      <c r="Q527" t="n">
-        <v>0.08699999999999999</v>
-      </c>
-      <c r="R527" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="S527" t="n">
-        <v>0.017</v>
-      </c>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B528" s="2" t="n">
-        <v>45040</v>
-      </c>
-      <c r="C528" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D528" t="n">
-        <v>3557</v>
-      </c>
-      <c r="E528" t="b">
-        <v>0</v>
-      </c>
-      <c r="F528" t="inlineStr"/>
-      <c r="G528" t="inlineStr"/>
-      <c r="H528" t="inlineStr"/>
-      <c r="I528" t="inlineStr"/>
-      <c r="J528" t="inlineStr"/>
-      <c r="K528" t="inlineStr"/>
-      <c r="L528" t="inlineStr"/>
-      <c r="M528" t="inlineStr"/>
-      <c r="N528" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="O528" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P528" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Q528" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R528" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S528" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B529" s="2" t="n">
-        <v>44999</v>
-      </c>
-      <c r="C529" t="inlineStr">
-        <is>
-          <t>Institute of Irish Studies</t>
-        </is>
-      </c>
-      <c r="D529" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E529" t="b">
-        <v>0</v>
-      </c>
-      <c r="F529" t="inlineStr"/>
-      <c r="G529" t="inlineStr"/>
-      <c r="H529" t="inlineStr"/>
-      <c r="I529" t="inlineStr"/>
-      <c r="J529" t="inlineStr"/>
-      <c r="K529" t="inlineStr"/>
-      <c r="L529" t="inlineStr"/>
-      <c r="M529" t="inlineStr"/>
-      <c r="N529" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="O529" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="P529" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="Q529" t="n">
-        <v>0.113</v>
-      </c>
-      <c r="R529" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="S529" t="n">
-        <v>0.048</v>
-      </c>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B530" s="2" t="n">
-        <v>44949</v>
-      </c>
-      <c r="C530" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D530" t="n">
-        <v>1499</v>
-      </c>
-      <c r="E530" t="b">
-        <v>0</v>
-      </c>
-      <c r="F530" t="inlineStr"/>
-      <c r="G530" t="inlineStr"/>
-      <c r="H530" t="inlineStr"/>
-      <c r="I530" t="inlineStr"/>
-      <c r="J530" t="inlineStr"/>
-      <c r="K530" t="inlineStr"/>
-      <c r="L530" t="inlineStr"/>
-      <c r="M530" t="inlineStr"/>
-      <c r="N530" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="O530" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P530" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q530" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="R530" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S530" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B531" s="2" t="n">
-        <v>44872</v>
-      </c>
-      <c r="C531" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D531" t="n">
-        <v>3351</v>
-      </c>
-      <c r="E531" t="b">
-        <v>0</v>
-      </c>
-      <c r="F531" t="inlineStr"/>
-      <c r="G531" t="inlineStr"/>
-      <c r="H531" t="inlineStr"/>
-      <c r="I531" t="inlineStr"/>
-      <c r="J531" t="inlineStr"/>
-      <c r="K531" t="inlineStr"/>
-      <c r="L531" t="inlineStr"/>
-      <c r="M531" t="inlineStr"/>
-      <c r="N531" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="O531" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="P531" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="Q531" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="R531" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S531" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B532" s="2" t="n">
-        <v>44788</v>
-      </c>
-      <c r="C532" t="inlineStr">
-        <is>
-          <t>LucidTalk</t>
-        </is>
-      </c>
-      <c r="D532" t="n">
-        <v>3384</v>
-      </c>
-      <c r="E532" t="b">
-        <v>0</v>
-      </c>
-      <c r="F532" t="inlineStr"/>
-      <c r="G532" t="inlineStr"/>
-      <c r="H532" t="inlineStr"/>
-      <c r="I532" t="inlineStr"/>
-      <c r="J532" t="inlineStr"/>
-      <c r="K532" t="inlineStr"/>
-      <c r="L532" t="inlineStr"/>
-      <c r="M532" t="inlineStr"/>
-      <c r="N532" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O532" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="P532" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="Q532" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="R532" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="S532" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B533" s="2" t="n">
-        <v>44752</v>
-      </c>
-      <c r="C533" t="inlineStr">
-        <is>
-          <t>Institute of Irish Studies</t>
-        </is>
-      </c>
-      <c r="D533" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E533" t="b">
-        <v>0</v>
-      </c>
-      <c r="F533" t="inlineStr"/>
-      <c r="G533" t="inlineStr"/>
-      <c r="H533" t="inlineStr"/>
-      <c r="I533" t="inlineStr"/>
-      <c r="J533" t="inlineStr"/>
-      <c r="K533" t="inlineStr"/>
-      <c r="L533" t="inlineStr"/>
-      <c r="M533" t="inlineStr"/>
-      <c r="N533" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="O533" t="n">
-        <v>0.201</v>
-      </c>
-      <c r="P533" t="n">
-        <v>0.153</v>
-      </c>
-      <c r="Q533" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="R533" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="S533" t="n">
-        <v>0.047</v>
-      </c>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr">
-        <is>
-          <t>NI</t>
-        </is>
-      </c>
-      <c r="B534" s="2" t="n">
-        <v>44686</v>
-      </c>
-      <c r="C534" t="inlineStr">
-        <is>
-          <t>2022 Assembly election</t>
-        </is>
-      </c>
-      <c r="D534" t="n">
-        <v>290</v>
-      </c>
-      <c r="E534" t="b">
-        <v>0</v>
-      </c>
-      <c r="F534" t="inlineStr"/>
-      <c r="G534" t="inlineStr"/>
-      <c r="H534" t="inlineStr"/>
-      <c r="I534" t="inlineStr"/>
-      <c r="J534" t="inlineStr"/>
-      <c r="K534" t="inlineStr"/>
-      <c r="L534" t="inlineStr"/>
-      <c r="M534" t="inlineStr"/>
-      <c r="N534" t="n">
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="n">
         <v>0.213</v>
       </c>
-      <c r="O534" t="n">
+      <c r="O481" t="n">
         <v>0.135</v>
       </c>
-      <c r="P534" t="n">
+      <c r="P481" t="n">
         <v>0.112</v>
       </c>
-      <c r="Q534" t="n">
+      <c r="Q481" t="n">
         <v>0.091</v>
       </c>
-      <c r="R534" t="n">
+      <c r="R481" t="n">
         <v>0.076</v>
       </c>
-      <c r="S534" t="n">
+      <c r="S481" t="n">
         <v>0.019</v>
       </c>
     </row>
